--- a/data/bench/benchmark_report.xlsx
+++ b/data/bench/benchmark_report.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Colors" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DPS Builds" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ALAC Builds" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="QUICK Builds" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DPS Builds" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALAC Builds" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUICK Builds" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colors" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DPS Builds'!$A$1:$G$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ALAC Builds'!$A$1:$G$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'QUICK Builds'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DPS Builds'!$A$1:$G$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALAC Builds'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QUICK Builds'!$A$1:$G$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,24 +48,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB3D9FF"/>
-        <bgColor rgb="FFB3D9FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
-        <bgColor rgb="FFFFFF99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF9933"/>
-        <bgColor rgb="FFFF9933"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF99FF99"/>
         <bgColor rgb="FF99FF99"/>
       </patternFill>
@@ -78,8 +60,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF6666"/>
-        <bgColor rgb="FFFF6666"/>
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,8 +72,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF6666"/>
+        <bgColor rgb="FFFF6666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9933"/>
+        <bgColor rgb="FFFF9933"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF33CC33"/>
         <bgColor rgb="FF33CC33"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,8 +102,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFB3D9FF"/>
+        <bgColor rgb="FFB3D9FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,9 +129,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,622 +497,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Color_Code</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Example</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Guardian</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FFB3D9FF</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Guardian</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Warrior</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>FFFFFF99</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Warrior</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>FFFF9933</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ranger</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>FF99FF99</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Ranger</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Thief</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FFB366FF</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Thief</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Elementalist</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FFFF6666</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Elementalist</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>Elite Spec</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mesmer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FFCC66FF</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Mesmer</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Necromancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FF33CC33</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Necromancer</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Evoker</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Elementalist</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Revenant</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FFFF9966</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Revenant</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Catalyst</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Elementalist</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Tempest</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Elementalist</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Weaver</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Elementalist</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Mechanist</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Amalgam</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Holosmith</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Scrapper</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Luminary</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Guardian</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Dragonhunter</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Guardian</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Willbender</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Guardian</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Mirage</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Mesmer</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Troubadour</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Mesmer</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Chronomancer</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Mesmer</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Virtuoso</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Mesmer</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Reaper</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>Necromancer</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Scourge</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Necromancer</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Ritualist</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>Necromancer</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Harbinger</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>Necromancer</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Soulbeast</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Ranger</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Galeshot</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Ranger</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Untamed</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Ranger</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Druid</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Ranger</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Vindicator</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>Revenant</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Herald</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>Revenant</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Renegade</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>Revenant</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Daredevil</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>Thief</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Thief</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>Thief</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Specter</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>Thief</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Deadeye</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>Thief</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Antiquary</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Thief</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Berserker</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Warrior</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Paragon</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Warrior</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Bladesworn</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Warrior</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Spellbreaker</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Warrior</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1162,7 +546,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Condition Druid Dagger Torch Axe Dagger</t>
         </is>
@@ -1197,7 +581,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Power Daredevil Dagger Dagger Axe Pistol</t>
         </is>
@@ -1232,7 +616,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Power Daredevil Dagger Only</t>
         </is>
@@ -1267,7 +651,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Power Antiquary Staff Dagger Pistol</t>
         </is>
@@ -1302,7 +686,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Power Berserker Axe Axe Sword Mace</t>
         </is>
@@ -1337,7 +721,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Power Antiquary Spear Axe Pistol</t>
         </is>
@@ -1372,7 +756,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Condition Mirage Ih Oasis Staff Axe Torch</t>
         </is>
@@ -1407,7 +791,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Condition Berserker Longbow Sword Torch</t>
         </is>
@@ -1442,7 +826,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Condition Evoker Specialized Elements</t>
         </is>
@@ -1477,7 +861,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Condition Weaver Pistol Dagger</t>
         </is>
@@ -1512,7 +896,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Power Amalgam Double Helix Hammer</t>
         </is>
@@ -1547,7 +931,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Condition Reaper Spear Dagger Sword</t>
         </is>
@@ -1582,7 +966,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Condition Antiquary Scepter Dagger</t>
         </is>
@@ -1617,7 +1001,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Condition Holosmith Pistol Pistol</t>
         </is>
@@ -1652,7 +1036,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Condition Weaver Scepter Warhorn</t>
         </is>
@@ -1687,7 +1071,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Power Chronomancer Greatsword Dagger Sword</t>
         </is>
@@ -1722,7 +1106,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Power Chronomancer Spear Dagger Sword</t>
         </is>
@@ -1792,7 +1176,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Condition Amalgam Steamshrieker Spear</t>
         </is>
@@ -1827,7 +1211,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Power Ritualist Greatsword Spear</t>
         </is>
@@ -1862,7 +1246,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Condition Weaver Pistol Warhorn</t>
         </is>
@@ -1897,7 +1281,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Power Vindicator Greatsword Sword Sword</t>
         </is>
@@ -1932,7 +1316,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Condition Evoker Pistol Dagger</t>
         </is>
@@ -1967,7 +1351,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Condition Chronomancer Staff Scepter Torch</t>
         </is>
@@ -2002,7 +1386,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Power Spellbreaker Dagger Mace Dagger Axe</t>
         </is>
@@ -2037,7 +1421,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Power Galeshot Longbow Axe Axe</t>
         </is>
@@ -2072,7 +1456,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Condition Soulbeast Shortbow Dagger Dagger</t>
         </is>
@@ -2107,7 +1491,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Power Bladesworn Faf Sword Pistol</t>
         </is>
@@ -2142,7 +1526,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Power Berserker Whirlpain Spear Greatsword</t>
         </is>
@@ -2177,7 +1561,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Power Renegade Greatsword Sword Sword</t>
         </is>
@@ -2212,7 +1596,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Condition Harbinger Pistol Torch Scepter Dagger</t>
         </is>
@@ -2247,7 +1631,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Condition Willbender Pistol Torch Pistol</t>
         </is>
@@ -2282,7 +1666,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Power Virtuoso Spear Greatsword</t>
         </is>
@@ -2317,7 +1701,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Power Scrapper Hammer</t>
         </is>
@@ -2352,7 +1736,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Power Paragon Sword Axe Dagger Mace</t>
         </is>
@@ -2387,7 +1771,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Power Amalgam Hammer</t>
         </is>
@@ -2422,7 +1806,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Condition Thief Axe Dagger Only</t>
         </is>
@@ -2457,7 +1841,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Condition Mechanist Two Kits Spear</t>
         </is>
@@ -2492,7 +1876,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Power Catalyst Scepter Dagger</t>
         </is>
@@ -2527,7 +1911,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Power Holosmith Sword Pistol</t>
         </is>
@@ -2562,7 +1946,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Power Dragonhunter Radiance Spear Greatsword</t>
         </is>
@@ -2597,7 +1981,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Power Antiquary Rifle Only</t>
         </is>
@@ -2632,7 +2016,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Condition Tempest Pistol Warhorn</t>
         </is>
@@ -2702,7 +2086,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>Power Harbinger Greatsword Spear</t>
         </is>
@@ -2737,7 +2121,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Condition Daredevil Dagger Only</t>
         </is>
@@ -2772,7 +2156,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>Power Evoker Scepter Dagger</t>
         </is>
@@ -2807,7 +2191,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Condition Willbender Scepter Pistol Pistol Torch</t>
         </is>
@@ -2842,7 +2226,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>Power Reaper Greatsword Spear</t>
         </is>
@@ -2877,7 +2261,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Power Tempest Spear</t>
         </is>
@@ -2912,7 +2296,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Power Tempest Sword Dagger</t>
         </is>
@@ -2947,7 +2331,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Condition Renegade Shortbow Mace Axe</t>
         </is>
@@ -2982,7 +2366,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Power Catalyst Spear</t>
         </is>
@@ -3017,7 +2401,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Power Berserker Hammer Axe Mace</t>
         </is>
@@ -3052,7 +2436,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Power Daredevil Sword Dagger Axe Pistol</t>
         </is>
@@ -3087,7 +2471,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Power Tempest Scepter Dagger</t>
         </is>
@@ -3122,7 +2506,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Power Berserker Tactics Spear Greatsword</t>
         </is>
@@ -3157,7 +2541,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Condition Daredevil Spear Axe Dagger</t>
         </is>
@@ -3192,7 +2576,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Condition Daredevil Spear Only</t>
         </is>
@@ -3227,7 +2611,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>Power Renegade Hammer Sword Sword</t>
         </is>
@@ -3297,7 +2681,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Power Troubadour Spear Greatsword</t>
         </is>
@@ -3332,7 +2716,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Power Mechanist Sword Pistol</t>
         </is>
@@ -3367,7 +2751,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>Power Weaver Spear</t>
         </is>
@@ -3402,7 +2786,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Condition Paragon Longbow Sword Sword</t>
         </is>
@@ -3437,7 +2821,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Power Daredevil Staff</t>
         </is>
@@ -3472,7 +2856,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>Power Willbender Spear Greatsword</t>
         </is>
@@ -3507,7 +2891,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Power Deadeye M7 Rifle Dagger Dagger</t>
         </is>
@@ -3542,7 +2926,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>Inferno Tempest Scepter Dagger</t>
         </is>
@@ -3577,7 +2961,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>Power Tempest Hammer</t>
         </is>
@@ -3612,7 +2996,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Power Weaver Sword Dagger</t>
         </is>
@@ -3647,7 +3031,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>Power Luminary Longbow Greatsword</t>
         </is>
@@ -3682,7 +3066,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t>Power Willbender Peitha Greatsword Sword Focus</t>
         </is>
@@ -3717,7 +3101,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>Condition Mechanist One Kit Spear</t>
         </is>
@@ -3752,7 +3136,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Condition Specter Scepter Dagger Only</t>
         </is>
@@ -3787,7 +3171,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>Power Luminary Spear Greatsword</t>
         </is>
@@ -3822,7 +3206,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>Power Reaper Greatsword Dagger Sword</t>
         </is>
@@ -3857,7 +3241,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>Power Reaper Greatsword Sword Sword</t>
         </is>
@@ -3892,7 +3276,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>Condition Scourge Scepter Torch Pistol</t>
         </is>
@@ -3962,7 +3346,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Power Soulbeast Hammer Axe Axe</t>
         </is>
@@ -3997,7 +3381,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Power Soulbeast Hammer Sword Axe</t>
         </is>
@@ -4032,7 +3416,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>Power Spellbreaker Hammer Dagger Mace</t>
         </is>
@@ -4067,7 +3451,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="11" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>Condition Renegade Spear Only</t>
         </is>
@@ -4102,7 +3486,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>Condition Virtuoso Dagger Sword Focus</t>
         </is>
@@ -4137,7 +3521,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>Condition Catalyst Pistol Dagger</t>
         </is>
@@ -4172,7 +3556,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>Power Mechanist Rifle</t>
         </is>
@@ -4207,7 +3591,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="11" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>Power Herald Staff Sword Sword</t>
         </is>
@@ -4242,7 +3626,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="7" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>Condition Quickness Evoker Specialized Elements</t>
         </is>
@@ -4282,7 +3666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4337,7 +3721,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Power Alacrity Antiquary Spear Axe Pistol</t>
         </is>
@@ -4372,7 +3756,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Power Alacrity Antiquary Staff Dagger Pistol</t>
         </is>
@@ -4407,7 +3791,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Condition Alacrity Antiquary Scepter Dagger Only</t>
         </is>
@@ -4442,7 +3826,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Condition Alacrity Mirage Staff Axe Torch</t>
         </is>
@@ -4477,7 +3861,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Condition Alacrity Evoker Pistol Warhorn</t>
         </is>
@@ -4512,7 +3896,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Condition Alacrity Amalgam Steamshrieker Spear</t>
         </is>
@@ -4547,7 +3931,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Power Alacrity Luminary Longbow Greatsword</t>
         </is>
@@ -4582,7 +3966,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Power Alacrity Luminary Spear Greatsword</t>
         </is>
@@ -4617,7 +4001,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Power Alacrity Antiquary Rifle Only</t>
         </is>
@@ -4652,7 +4036,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Power Alacrity Bladesworn Overcharged Cartridges Sword Pistol</t>
         </is>
@@ -4687,7 +4071,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Power Boon Chronomancer Spear Dagger Sword</t>
         </is>
@@ -4722,7 +4106,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Power Alacrity Amalgam Hammer</t>
         </is>
@@ -4757,7 +4141,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Condition Alacrity Specter Spear Only</t>
         </is>
@@ -4792,7 +4176,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Power Boon Chronomancer Greatsword Spear</t>
         </is>
@@ -4827,7 +4211,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Power Boon Chronomancer Greatsword Dagger Sword</t>
         </is>
@@ -4862,7 +4246,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Power Alacrity Bladesworn Signets Sword Pistol</t>
         </is>
@@ -4897,7 +4281,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Condition Boon Chronomancer Staff Scepter Torch</t>
         </is>
@@ -4932,7 +4316,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Condition Alacrity Renegade Spear Mace Axe</t>
         </is>
@@ -4967,7 +4351,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Condition Alacrity Renegade Shortbow Mace Axe</t>
         </is>
@@ -5002,7 +4386,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Power Alacrity Tempest Hammer</t>
         </is>
@@ -5037,7 +4421,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Power Alacrity Mechanist Two Kits Sword Pistol</t>
         </is>
@@ -5072,7 +4456,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Power Alacrity Evoker Scepter Dagger</t>
         </is>
@@ -5107,7 +4491,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Condition Alacrity Specter Scepter Dagger Dagger</t>
         </is>
@@ -5142,7 +4526,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Power Alacrity Renegade Greatsword Sword Sword</t>
         </is>
@@ -5177,7 +4561,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Condition Alacrity Renegade Spear Only</t>
         </is>
@@ -5212,7 +4596,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Power Alacrity Renegade Staff Sword Sword</t>
         </is>
@@ -5247,7 +4631,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Power Alacrity Tempest Sword Dagger</t>
         </is>
@@ -5282,7 +4666,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Condition Alacrity Scourge Scepter Torch Pistol</t>
         </is>
@@ -5317,7 +4701,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Power Boon Chronomancer Greatsword Dagger Focus</t>
         </is>
@@ -5352,7 +4736,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Power Alacrity Willbender Greatsword Sword Focus</t>
         </is>
@@ -5387,7 +4771,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Power Alacrity Willbender Spear Greatsword</t>
         </is>
@@ -5422,7 +4806,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Power Alacrity Mechanist Rifle</t>
         </is>
@@ -5457,7 +4841,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Celestial Alacrity Tempest Scepter Warhorn</t>
         </is>
@@ -5497,7 +4881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5552,7 +4936,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Condition Quickness Evoker Specialized Elements</t>
         </is>
@@ -5587,7 +4971,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Power Quickness Evoker Scepter Dagger</t>
         </is>
@@ -5622,7 +5006,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Power Quickness Deadeye Axe Pistol Dagger</t>
         </is>
@@ -5657,7 +5041,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Condition Quickness Berserker Longbow Sword Torch</t>
         </is>
@@ -5692,7 +5076,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Power Quickness Deadeye Dagger Only</t>
         </is>
@@ -5727,7 +5111,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Power Quickness Berserker Tactics Spear Greatsword</t>
         </is>
@@ -5762,7 +5146,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Power Quickness Ritualist Greatsword Spear</t>
         </is>
@@ -5797,7 +5181,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Condition Quickness Harbinger Pistol Dagger Scepter Torch</t>
         </is>
@@ -5832,7 +5216,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Power Boon Chronomancer Spear Dagger Sword</t>
         </is>
@@ -5867,7 +5251,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Power Quickness Galeshot Longbow Axe Axe</t>
         </is>
@@ -5902,7 +5286,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Power Quickness Untamed Hammer Sword Axe</t>
         </is>
@@ -5937,7 +5321,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Power Quickness Berserker Greatsword Axe Axe</t>
         </is>
@@ -5972,7 +5356,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Power Quickness Berserker Spear Axe Axe</t>
         </is>
@@ -6007,7 +5391,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Power Quickness Catalyst Scepter Dagger</t>
         </is>
@@ -6042,7 +5426,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Condition Quickness Untamed Axe Dagger Dagger Torch</t>
         </is>
@@ -6077,7 +5461,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Condition Quickness Scrapper Spear</t>
         </is>
@@ -6147,7 +5531,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Power Quickness Untamed Nature Magic Hammer Sword Axe</t>
         </is>
@@ -6182,7 +5566,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Condition Quickness Deadeye Spear Only</t>
         </is>
@@ -6252,7 +5636,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Power Quickness Catalyst Sword Dagger</t>
         </is>
@@ -6287,7 +5671,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Power Quickness Harbinger Greatsword Spear</t>
         </is>
@@ -6322,7 +5706,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Condition Quickness Catalyst Pistol Dagger</t>
         </is>
@@ -6357,7 +5741,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Power Quickness Troubadour Spear Dagger Sword</t>
         </is>
@@ -6392,7 +5776,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Power Quickness Deadeye Spear Only</t>
         </is>
@@ -6427,7 +5811,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Power Quickness Herald Greatsword Sword Sword</t>
         </is>
@@ -6462,7 +5846,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Condition Quickness Herald Spear Mace Axe</t>
         </is>
@@ -6497,7 +5881,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Condition Quickness Herald Shortbow Mace Axe</t>
         </is>
@@ -6532,7 +5916,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Power Quickness Herald Staff Sword Sword</t>
         </is>
@@ -6567,7 +5951,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Condition Quickness Herald Spear Only</t>
         </is>
@@ -6605,4 +5989,188 @@
   <autoFilter ref="A1:G31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Profession</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Color_Code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FFB3D9FF</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Guardian</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FFFFFF99</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FFFF9933</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ranger</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FF99FF99</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Ranger</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Thief</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FFB366FF</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Thief</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Elementalist</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FFFF6666</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Elementalist</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mesmer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FFCC66FF</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Mesmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Necromancer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FF33CC33</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Necromancer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Revenant</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FFFF9966</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Revenant</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/bench/benchmark_report.xlsx
+++ b/data/bench/benchmark_report.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colors" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DPS Builds'!$A$1:$G$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALAC Builds'!$A$1:$G$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QUICK Builds'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DPS Builds'!$A$1:$G$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ALAC Builds'!$A$1:$G$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QUICK Builds'!$A$1:$G$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99FF99"/>
-        <bgColor rgb="FF99FF99"/>
+        <fgColor rgb="FFB366FF"/>
+        <bgColor rgb="FFB366FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB366FF"/>
-        <bgColor rgb="FFB366FF"/>
+        <fgColor rgb="FF99FF99"/>
+        <bgColor rgb="FF99FF99"/>
       </patternFill>
     </fill>
     <fill>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
@@ -548,7 +548,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Condition Druid Dagger Torch Axe Dagger</t>
+          <t>Condition Antiquary Spear Only</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>44667</v>
+        <v>45298</v>
       </c>
       <c r="E2">
         <f>ROUND(C2/D2*100,2)</f>
@@ -576,26 +576,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Power Daredevil Dagger Dagger Axe Pistol</t>
+          <t>Condition Druid Dagger Torch Axe Dagger</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>44282</v>
+        <v>44667</v>
       </c>
       <c r="E3">
         <f>ROUND(C3/D3*100,2)</f>
@@ -611,14 +611,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Power Daredevil Dagger Only</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Power Daredevil Dagger Dagger Axe Pistol</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,9 +651,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Power Antiquary Staff Dagger Pistol</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Power Daredevil Dagger Only</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>44271</v>
+        <v>44282</v>
       </c>
       <c r="E5">
         <f>ROUND(C5/D5*100,2)</f>
@@ -686,9 +686,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Power Berserker Axe Axe Sword Mace</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Power Antiquary Staff Dagger Pistol</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>44256</v>
+        <v>44271</v>
       </c>
       <c r="E6">
         <f>ROUND(C6/D6*100,2)</f>
@@ -716,14 +716,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Power Antiquary Spear Axe Pistol</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Power Berserker Axe Axe Sword Mace</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -735,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>44233</v>
+        <v>44256</v>
       </c>
       <c r="E7">
         <f>ROUND(C7/D7*100,2)</f>
@@ -751,26 +751,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Condition Mirage Ih Oasis Staff Axe Torch</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Power Antiquary Spear Axe Pistol</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>44170</v>
+        <v>44233</v>
       </c>
       <c r="E8">
         <f>ROUND(C8/D8*100,2)</f>
@@ -786,14 +786,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Condition Berserker Longbow Sword Torch</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Condition Mirage Ih Oasis Staff Axe Torch</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>44151</v>
+        <v>44170</v>
       </c>
       <c r="E9">
         <f>ROUND(C9/D9*100,2)</f>
@@ -821,14 +821,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Condition Evoker Specialized Elements</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Condition Berserker Longbow Sword Torch</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>44135</v>
+        <v>44151</v>
       </c>
       <c r="E10">
         <f>ROUND(C10/D10*100,2)</f>
@@ -856,14 +856,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Condition Weaver Pistol Dagger</t>
+          <t>Condition Evoker Specialized Elements</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>43829</v>
+        <v>44135</v>
       </c>
       <c r="E11">
         <f>ROUND(C11/D11*100,2)</f>
@@ -896,21 +896,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Power Amalgam Double Helix Hammer</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Condition Weaver Pistol Dagger</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>43571</v>
+        <v>43829</v>
       </c>
       <c r="E12">
         <f>ROUND(C12/D12*100,2)</f>
@@ -926,14 +926,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Condition Reaper Spear Dagger Sword</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Condition Mirage Ih Ether Staff Axe Torch</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -945,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>43537</v>
+        <v>43608</v>
       </c>
       <c r="E13">
         <f>ROUND(C13/D13*100,2)</f>
@@ -961,26 +961,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Condition Antiquary Scepter Dagger</t>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Power Amalgam Double Helix Hammer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>43451</v>
+        <v>43571</v>
       </c>
       <c r="E14">
         <f>ROUND(C14/D14*100,2)</f>
@@ -996,14 +996,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Condition Holosmith Pistol Pistol</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Condition Reaper Spear Dagger Sword</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>43198</v>
+        <v>43537</v>
       </c>
       <c r="E15">
         <f>ROUND(C15/D15*100,2)</f>
@@ -1031,14 +1031,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Condition Weaver Scepter Warhorn</t>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Condition Amalgam Three Kits Spear</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>43155</v>
+        <v>43533</v>
       </c>
       <c r="E16">
         <f>ROUND(C16/D16*100,2)</f>
@@ -1066,26 +1066,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Power Chronomancer Greatsword Dagger Sword</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Condition Antiquary Scepter Dagger</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>43075</v>
+        <v>43451</v>
       </c>
       <c r="E17">
         <f>ROUND(C17/D17*100,2)</f>
@@ -1101,26 +1101,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Power Chronomancer Spear Dagger Sword</t>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Condition Holosmith Pistol Pistol</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>43072</v>
+        <v>43198</v>
       </c>
       <c r="E18">
         <f>ROUND(C18/D18*100,2)</f>
@@ -1136,26 +1136,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Power Conduit Greatsword Scepter Sword</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Condition Weaver Scepter Warhorn</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>42939</v>
+        <v>43155</v>
       </c>
       <c r="E19">
         <f>ROUND(C19/D19*100,2)</f>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Condition Amalgam Steamshrieker Spear</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Power Chronomancer Greatsword Dagger Sword</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>42824</v>
+        <v>43075</v>
       </c>
       <c r="E20">
         <f>ROUND(C20/D20*100,2)</f>
@@ -1206,14 +1206,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Power Ritualist Greatsword Spear</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Power Chronomancer Spear Dagger Sword</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1225,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>42712</v>
+        <v>43072</v>
       </c>
       <c r="E21">
         <f>ROUND(C21/D21*100,2)</f>
@@ -1241,26 +1241,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Condition Weaver Pistol Warhorn</t>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Power Conduit Greatsword Scepter Sword</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>42706</v>
+        <v>42939</v>
       </c>
       <c r="E22">
         <f>ROUND(C22/D22*100,2)</f>
@@ -1276,26 +1276,26 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Power Vindicator Greatsword Sword Sword</t>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Condition Amalgam Steamshrieker Spear</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>42670</v>
+        <v>42824</v>
       </c>
       <c r="E23">
         <f>ROUND(C23/D23*100,2)</f>
@@ -1311,26 +1311,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Condition Evoker Pistol Dagger</t>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Power Ritualist Greatsword Spear</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>42665</v>
+        <v>42712</v>
       </c>
       <c r="E24">
         <f>ROUND(C24/D24*100,2)</f>
@@ -1346,14 +1346,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Condition Chronomancer Staff Scepter Torch</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Condition Weaver Pistol Warhorn</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1365,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>42653</v>
+        <v>42706</v>
       </c>
       <c r="E25">
         <f>ROUND(C25/D25*100,2)</f>
@@ -1381,14 +1381,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Power Spellbreaker Dagger Mace Dagger Axe</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Power Untamed Beastmastery Hammer Sword Axe</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>42633</v>
+        <v>42705</v>
       </c>
       <c r="E26">
         <f>ROUND(C26/D26*100,2)</f>
@@ -1416,14 +1416,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Power Galeshot Longbow Axe Axe</t>
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Power Vindicator Greatsword Sword Sword</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>42575</v>
+        <v>42670</v>
       </c>
       <c r="E27">
         <f>ROUND(C27/D27*100,2)</f>
@@ -1451,14 +1451,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Condition Soulbeast Shortbow Dagger Dagger</t>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Condition Evoker Pistol Dagger</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1470,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>42481</v>
+        <v>42665</v>
       </c>
       <c r="E28">
         <f>ROUND(C28/D28*100,2)</f>
@@ -1486,26 +1486,26 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Power Bladesworn Faf Sword Pistol</t>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Condition Chronomancer Staff Scepter Torch</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>42457</v>
+        <v>42653</v>
       </c>
       <c r="E29">
         <f>ROUND(C29/D29*100,2)</f>
@@ -1521,14 +1521,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Power Berserker Whirlpain Spear Greatsword</t>
+          <t>Power Spellbreaker Dagger Mace Dagger Axe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>42362</v>
+        <v>42633</v>
       </c>
       <c r="E30">
         <f>ROUND(C30/D30*100,2)</f>
@@ -1561,9 +1561,9 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Power Renegade Greatsword Sword Sword</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Power Galeshot Longbow Axe Axe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>42297</v>
+        <v>42575</v>
       </c>
       <c r="E31">
         <f>ROUND(C31/D31*100,2)</f>
@@ -1591,14 +1591,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Condition Harbinger Pistol Torch Scepter Dagger</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Condition Soulbeast Shortbow Dagger Dagger</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>42276</v>
+        <v>42481</v>
       </c>
       <c r="E32">
         <f>ROUND(C32/D32*100,2)</f>
@@ -1626,26 +1626,26 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>Condition Willbender Pistol Torch Pistol</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Power Bladesworn Faf Sword Pistol</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>42265</v>
+        <v>42457</v>
       </c>
       <c r="E33">
         <f>ROUND(C33/D33*100,2)</f>
@@ -1661,14 +1661,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Power Virtuoso Spear Greatsword</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Power Berserker Whirlpain Spear Greatsword</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>42218</v>
+        <v>42362</v>
       </c>
       <c r="E34">
         <f>ROUND(C34/D34*100,2)</f>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Power Scrapper Hammer</t>
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Power Renegade Greatsword Sword Sword</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1715,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>42205</v>
+        <v>42297</v>
       </c>
       <c r="E35">
         <f>ROUND(C35/D35*100,2)</f>
@@ -1731,26 +1731,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Power Paragon Sword Axe Dagger Mace</t>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Condition Harbinger Pistol Torch Scepter Dagger</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>42187</v>
+        <v>42276</v>
       </c>
       <c r="E36">
         <f>ROUND(C36/D36*100,2)</f>
@@ -1766,26 +1766,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Power Amalgam Hammer</t>
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Condition Willbender Pistol Torch Pistol</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>42170</v>
+        <v>42265</v>
       </c>
       <c r="E37">
         <f>ROUND(C37/D37*100,2)</f>
@@ -1801,26 +1801,26 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Condition Thief Axe Dagger Only</t>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Power Virtuoso Spear Greatsword</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>42108</v>
+        <v>42218</v>
       </c>
       <c r="E38">
         <f>ROUND(C38/D38*100,2)</f>
@@ -1836,26 +1836,26 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Condition Mechanist Two Kits Spear</t>
+          <t>Power Scrapper Hammer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>42018</v>
+        <v>42205</v>
       </c>
       <c r="E39">
         <f>ROUND(C39/D39*100,2)</f>
@@ -1876,9 +1876,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Power Catalyst Scepter Dagger</t>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Power Paragon Sword Axe Dagger Mace</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>42006</v>
+        <v>42187</v>
       </c>
       <c r="E40">
         <f>ROUND(C40/D40*100,2)</f>
@@ -1906,14 +1906,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Power Holosmith Sword Pistol</t>
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Power Dragonhunter Radiance Longbow Greatsword</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>41981</v>
+        <v>42179</v>
       </c>
       <c r="E41">
         <f>ROUND(C41/D41*100,2)</f>
@@ -1941,14 +1941,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>Power Dragonhunter Radiance Spear Greatsword</t>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Power Amalgam Hammer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>41879</v>
+        <v>42170</v>
       </c>
       <c r="E42">
         <f>ROUND(C42/D42*100,2)</f>
@@ -1976,26 +1976,26 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Power Antiquary Rifle Only</t>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Condition Thief Axe Dagger Only</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>41818</v>
+        <v>42108</v>
       </c>
       <c r="E43">
         <f>ROUND(C43/D43*100,2)</f>
@@ -2016,9 +2016,9 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Condition Tempest Pistol Warhorn</t>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Condition Mechanist Two Kits Spear</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>41703</v>
+        <v>42018</v>
       </c>
       <c r="E44">
         <f>ROUND(C44/D44*100,2)</f>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>Condition Conduit Spear Mace Axe</t>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Power Catalyst Scepter Dagger</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>41698</v>
+        <v>42006</v>
       </c>
       <c r="E45">
         <f>ROUND(C45/D45*100,2)</f>
@@ -2081,14 +2081,14 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Power Harbinger Greatsword Spear</t>
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Power Holosmith Sword Pistol</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>41692</v>
+        <v>41981</v>
       </c>
       <c r="E46">
         <f>ROUND(C46/D46*100,2)</f>
@@ -2116,14 +2116,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Condition Daredevil Dagger Only</t>
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Condition Renegade Spear Mace Axe</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2135,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>41689</v>
+        <v>41900</v>
       </c>
       <c r="E47">
         <f>ROUND(C47/D47*100,2)</f>
@@ -2151,14 +2151,14 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Power Evoker Scepter Dagger</t>
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Power Dragonhunter Radiance Spear Greatsword</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>41646</v>
+        <v>41879</v>
       </c>
       <c r="E48">
         <f>ROUND(C48/D48*100,2)</f>
@@ -2186,26 +2186,26 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Condition Willbender Scepter Pistol Pistol Torch</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Power Antiquary Rifle Only</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>41590</v>
+        <v>41818</v>
       </c>
       <c r="E49">
         <f>ROUND(C49/D49*100,2)</f>
@@ -2221,26 +2221,26 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Power Reaper Greatsword Spear</t>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Condition Tempest Pistol Warhorn</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>41533</v>
+        <v>41703</v>
       </c>
       <c r="E50">
         <f>ROUND(C50/D50*100,2)</f>
@@ -2256,26 +2256,26 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Power Tempest Spear</t>
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Condition Conduit Spear Mace Axe</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>41514</v>
+        <v>41698</v>
       </c>
       <c r="E51">
         <f>ROUND(C51/D51*100,2)</f>
@@ -2291,14 +2291,14 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Power Tempest Sword Dagger</t>
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Power Harbinger Greatsword Spear</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>41502</v>
+        <v>41692</v>
       </c>
       <c r="E52">
         <f>ROUND(C52/D52*100,2)</f>
@@ -2326,14 +2326,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>Condition Renegade Shortbow Mace Axe</t>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Condition Daredevil Dagger Only</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>41500</v>
+        <v>41689</v>
       </c>
       <c r="E53">
         <f>ROUND(C53/D53*100,2)</f>
@@ -2361,26 +2361,26 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Power Catalyst Spear</t>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Condition Specter Spear Only</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>41454</v>
+        <v>41653</v>
       </c>
       <c r="E54">
         <f>ROUND(C54/D54*100,2)</f>
@@ -2396,14 +2396,14 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Power Berserker Hammer Axe Mace</t>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Power Evoker Scepter Dagger</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>41418</v>
+        <v>41646</v>
       </c>
       <c r="E55">
         <f>ROUND(C55/D55*100,2)</f>
@@ -2431,26 +2431,26 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Power Daredevil Sword Dagger Axe Pistol</t>
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>Condition Willbender Scepter Pistol Pistol Torch</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>41321</v>
+        <v>41590</v>
       </c>
       <c r="E56">
         <f>ROUND(C56/D56*100,2)</f>
@@ -2466,14 +2466,14 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Power Tempest Scepter Dagger</t>
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Power Reaper Greatsword Spear</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>41321</v>
+        <v>41533</v>
       </c>
       <c r="E57">
         <f>ROUND(C57/D57*100,2)</f>
@@ -2501,14 +2501,14 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Power Berserker Tactics Spear Greatsword</t>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Power Tempest Spear</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>41315</v>
+        <v>41514</v>
       </c>
       <c r="E58">
         <f>ROUND(C58/D58*100,2)</f>
@@ -2536,26 +2536,26 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Condition Daredevil Spear Axe Dagger</t>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Power Tempest Sword Dagger</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>41302</v>
+        <v>41502</v>
       </c>
       <c r="E59">
         <f>ROUND(C59/D59*100,2)</f>
@@ -2571,14 +2571,14 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Condition Daredevil Spear Only</t>
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>Condition Renegade Shortbow Mace Axe</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>41302</v>
+        <v>41500</v>
       </c>
       <c r="E60">
         <f>ROUND(C60/D60*100,2)</f>
@@ -2606,14 +2606,14 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>Power Renegade Hammer Sword Sword</t>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Power Catalyst Spear</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2625,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>41300</v>
+        <v>41454</v>
       </c>
       <c r="E61">
         <f>ROUND(C61/D61*100,2)</f>
@@ -2641,14 +2641,14 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>Power Conduit Staff Sword Sword</t>
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Power Berserker Hammer Axe Mace</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2660,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>41217</v>
+        <v>41418</v>
       </c>
       <c r="E62">
         <f>ROUND(C62/D62*100,2)</f>
@@ -2676,14 +2676,14 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Power Troubadour Spear Greatsword</t>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Power Daredevil Sword Dagger Axe Pistol</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>41144</v>
+        <v>41321</v>
       </c>
       <c r="E63">
         <f>ROUND(C63/D63*100,2)</f>
@@ -2711,14 +2711,14 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Power Mechanist Sword Pistol</t>
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Power Tempest Scepter Dagger</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>41141</v>
+        <v>41321</v>
       </c>
       <c r="E64">
         <f>ROUND(C64/D64*100,2)</f>
@@ -2746,14 +2746,14 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Power Weaver Spear</t>
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Power Berserker Tactics Spear Greatsword</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>41118</v>
+        <v>41315</v>
       </c>
       <c r="E65">
         <f>ROUND(C65/D65*100,2)</f>
@@ -2781,14 +2781,14 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>Condition Paragon Longbow Sword Sword</t>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Condition Daredevil Spear Axe Dagger</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>41080</v>
+        <v>41302</v>
       </c>
       <c r="E66">
         <f>ROUND(C66/D66*100,2)</f>
@@ -2816,26 +2816,26 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Power Daredevil Staff</t>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Condition Daredevil Spear Only</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>41055</v>
+        <v>41302</v>
       </c>
       <c r="E67">
         <f>ROUND(C67/D67*100,2)</f>
@@ -2856,9 +2856,9 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>Power Willbender Spear Greatsword</t>
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Power Renegade Hammer Sword Sword</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>41009</v>
+        <v>41300</v>
       </c>
       <c r="E68">
         <f>ROUND(C68/D68*100,2)</f>
@@ -2886,14 +2886,14 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Power Deadeye M7 Rifle Dagger Dagger</t>
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>Power Conduit Staff Sword Sword</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2905,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>40923</v>
+        <v>41217</v>
       </c>
       <c r="E69">
         <f>ROUND(C69/D69*100,2)</f>
@@ -2921,14 +2921,14 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>Inferno Tempest Scepter Dagger</t>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Power Troubadour Spear Greatsword</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>40920</v>
+        <v>41144</v>
       </c>
       <c r="E70">
         <f>ROUND(C70/D70*100,2)</f>
@@ -2956,14 +2956,14 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Power Tempest Hammer</t>
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Power Mechanist Sword Pistol</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>40791</v>
+        <v>41141</v>
       </c>
       <c r="E71">
         <f>ROUND(C71/D71*100,2)</f>
@@ -2991,14 +2991,14 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Power Weaver Sword Dagger</t>
+          <t>Power Weaver Spear</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>40782</v>
+        <v>41118</v>
       </c>
       <c r="E72">
         <f>ROUND(C72/D72*100,2)</f>
@@ -3031,21 +3031,21 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>Power Luminary Longbow Greatsword</t>
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Condition Paragon Longbow Sword Sword</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>40774</v>
+        <v>41080</v>
       </c>
       <c r="E73">
         <f>ROUND(C73/D73*100,2)</f>
@@ -3061,14 +3061,14 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>Power Willbender Peitha Greatsword Sword Focus</t>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Power Daredevil Staff</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>40746</v>
+        <v>41055</v>
       </c>
       <c r="E74">
         <f>ROUND(C74/D74*100,2)</f>
@@ -3096,26 +3096,26 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>Condition Mechanist One Kit Spear</t>
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>Power Willbender Spear Greatsword</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>40667</v>
+        <v>41009</v>
       </c>
       <c r="E75">
         <f>ROUND(C75/D75*100,2)</f>
@@ -3131,26 +3131,26 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>Condition Specter Scepter Dagger Only</t>
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Inferno Catalyst Scepter Dagger</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>40628</v>
+        <v>40976</v>
       </c>
       <c r="E76">
         <f>ROUND(C76/D76*100,2)</f>
@@ -3166,14 +3166,14 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>Power Luminary Spear Greatsword</t>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Power Deadeye M7 Rifle Dagger Dagger</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>40557</v>
+        <v>40923</v>
       </c>
       <c r="E77">
         <f>ROUND(C77/D77*100,2)</f>
@@ -3201,14 +3201,14 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>Power Reaper Greatsword Dagger Sword</t>
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Inferno Tempest Scepter Dagger</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3220,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>40410</v>
+        <v>40920</v>
       </c>
       <c r="E78">
         <f>ROUND(C78/D78*100,2)</f>
@@ -3236,14 +3236,14 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>Power Reaper Greatsword Sword Sword</t>
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Power Tempest Hammer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3255,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>40366</v>
+        <v>40791</v>
       </c>
       <c r="E79">
         <f>ROUND(C79/D79*100,2)</f>
@@ -3271,26 +3271,26 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>Condition Scourge Scepter Torch Pistol</t>
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Power Weaver Sword Dagger</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>40060</v>
+        <v>40782</v>
       </c>
       <c r="E80">
         <f>ROUND(C80/D80*100,2)</f>
@@ -3306,26 +3306,26 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>Condition Conduit Mistfire Spear Mace Axe</t>
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>Power Luminary Longbow Greatsword</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>39982</v>
+        <v>40774</v>
       </c>
       <c r="E81">
         <f>ROUND(C81/D81*100,2)</f>
@@ -3341,14 +3341,14 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Power Soulbeast Hammer Axe Axe</t>
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>Power Willbender Peitha Greatsword Sword Focus</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3360,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>39871</v>
+        <v>40746</v>
       </c>
       <c r="E82">
         <f>ROUND(C82/D82*100,2)</f>
@@ -3376,26 +3376,26 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Power Soulbeast Hammer Sword Axe</t>
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Condition Mechanist One Kit Spear</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>39858</v>
+        <v>40667</v>
       </c>
       <c r="E83">
         <f>ROUND(C83/D83*100,2)</f>
@@ -3411,26 +3411,26 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Power Spellbreaker Hammer Dagger Mace</t>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Condition Specter Scepter Dagger Only</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>39709</v>
+        <v>40628</v>
       </c>
       <c r="E84">
         <f>ROUND(C84/D84*100,2)</f>
@@ -3446,26 +3446,26 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>Condition Renegade Spear Only</t>
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>Power Luminary Spear Greatsword</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>39480</v>
+        <v>40557</v>
       </c>
       <c r="E85">
         <f>ROUND(C85/D85*100,2)</f>
@@ -3481,14 +3481,14 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>Condition Virtuoso Dagger Sword Focus</t>
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Condition Tempest Scepter Warhorn</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3500,7 +3500,7 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>39115</v>
+        <v>40470</v>
       </c>
       <c r="E86">
         <f>ROUND(C86/D86*100,2)</f>
@@ -3516,26 +3516,26 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>Condition Catalyst Pistol Dagger</t>
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>Power Reaper Greatsword Dagger Sword</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>38625</v>
+        <v>40410</v>
       </c>
       <c r="E87">
         <f>ROUND(C87/D87*100,2)</f>
@@ -3551,14 +3551,14 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>Power Mechanist Rifle</t>
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>Power Reaper Greatsword Sword Sword</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>38473</v>
+        <v>40366</v>
       </c>
       <c r="E88">
         <f>ROUND(C88/D88*100,2)</f>
@@ -3586,14 +3586,14 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>Power Herald Staff Sword Sword</t>
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Power Catalyst Sword Dagger</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3605,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>36921</v>
+        <v>40189</v>
       </c>
       <c r="E89">
         <f>ROUND(C89/D89*100,2)</f>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>Condition Quickness Evoker Specialized Elements</t>
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>Condition Scourge Scepter Torch Pistol</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3640,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>40060</v>
       </c>
       <c r="E90">
         <f>ROUND(C90/D90*100,2)</f>
@@ -3656,12 +3656,502 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
+          <t>necromancer</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>Condition Conduit Mistfire Spear Mace Axe</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>39982</v>
+      </c>
+      <c r="E91">
+        <f>ROUND(C91/D91*100,2)</f>
+        <v/>
+      </c>
+      <c r="F91">
+        <f>ROUND(D91*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G91">
+        <f>ROUND(F91-C91,0)</f>
+        <v/>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Power Soulbeast Hammer Axe Axe</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>39871</v>
+      </c>
+      <c r="E92">
+        <f>ROUND(C92/D92*100,2)</f>
+        <v/>
+      </c>
+      <c r="F92">
+        <f>ROUND(D92*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G92">
+        <f>ROUND(F92-C92,0)</f>
+        <v/>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ranger</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Power Soulbeast Hammer Sword Axe</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>39858</v>
+      </c>
+      <c r="E93">
+        <f>ROUND(C93/D93*100,2)</f>
+        <v/>
+      </c>
+      <c r="F93">
+        <f>ROUND(D93*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G93">
+        <f>ROUND(F93-C93,0)</f>
+        <v/>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ranger</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Power Virtuoso Greatsword Dagger Sword</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>39813</v>
+      </c>
+      <c r="E94">
+        <f>ROUND(C94/D94*100,2)</f>
+        <v/>
+      </c>
+      <c r="F94">
+        <f>ROUND(D94*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G94">
+        <f>ROUND(F94-C94,0)</f>
+        <v/>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>mesmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Power Spellbreaker Hammer Dagger Mace</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>39709</v>
+      </c>
+      <c r="E95">
+        <f>ROUND(C95/D95*100,2)</f>
+        <v/>
+      </c>
+      <c r="F95">
+        <f>ROUND(D95*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G95">
+        <f>ROUND(F95-C95,0)</f>
+        <v/>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>warrior</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>Condition Renegade Spear Only</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>39480</v>
+      </c>
+      <c r="E96">
+        <f>ROUND(C96/D96*100,2)</f>
+        <v/>
+      </c>
+      <c r="F96">
+        <f>ROUND(D96*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G96">
+        <f>ROUND(F96-C96,0)</f>
+        <v/>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>revenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Power Virtuoso Spear Dagger Sword</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>39346</v>
+      </c>
+      <c r="E97">
+        <f>ROUND(C97/D97*100,2)</f>
+        <v/>
+      </c>
+      <c r="F97">
+        <f>ROUND(D97*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G97">
+        <f>ROUND(F97-C97,0)</f>
+        <v/>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>mesmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Condition Virtuoso Dagger Sword Focus</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>39115</v>
+      </c>
+      <c r="E98">
+        <f>ROUND(C98/D98*100,2)</f>
+        <v/>
+      </c>
+      <c r="F98">
+        <f>ROUND(D98*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G98">
+        <f>ROUND(F98-C98,0)</f>
+        <v/>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>mesmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Condition Catalyst Pistol Dagger</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>38625</v>
+      </c>
+      <c r="E99">
+        <f>ROUND(C99/D99*100,2)</f>
+        <v/>
+      </c>
+      <c r="F99">
+        <f>ROUND(D99*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G99">
+        <f>ROUND(F99-C99,0)</f>
+        <v/>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
           <t>elementalist</t>
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>Power Mechanist Rifle</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>38473</v>
+      </c>
+      <c r="E100">
+        <f>ROUND(C100/D100*100,2)</f>
+        <v/>
+      </c>
+      <c r="F100">
+        <f>ROUND(D100*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G100">
+        <f>ROUND(F100-C100,0)</f>
+        <v/>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Condition Mechanist No Kit Spear</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>38365</v>
+      </c>
+      <c r="E101">
+        <f>ROUND(C101/D101*100,2)</f>
+        <v/>
+      </c>
+      <c r="F101">
+        <f>ROUND(D101*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G101">
+        <f>ROUND(F101-C101,0)</f>
+        <v/>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Power Warrior Mace Axe Dagger Mace</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>37398</v>
+      </c>
+      <c r="E102">
+        <f>ROUND(C102/D102*100,2)</f>
+        <v/>
+      </c>
+      <c r="F102">
+        <f>ROUND(D102*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G102">
+        <f>ROUND(F102-C102,0)</f>
+        <v/>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>warrior</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>Power Herald Staff Sword Sword</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>36921</v>
+      </c>
+      <c r="E103">
+        <f>ROUND(C103/D103*100,2)</f>
+        <v/>
+      </c>
+      <c r="F103">
+        <f>ROUND(D103*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G103">
+        <f>ROUND(F103-C103,0)</f>
+        <v/>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>revenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Condition Quickness Evoker Specialized Elements</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <f>ROUND(C104/D104*100,2)</f>
+        <v/>
+      </c>
+      <c r="F104">
+        <f>ROUND(D104*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G104">
+        <f>ROUND(F104-C104,0)</f>
+        <v/>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>elementalist</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G90"/>
+  <autoFilter ref="A1:G104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3672,7 +4162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
@@ -3721,21 +4211,21 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Power Alacrity Antiquary Spear Axe Pistol</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Antiquary Spear Only</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>38528</v>
+        <v>40151</v>
       </c>
       <c r="E2">
         <f>ROUND(C2/D2*100,2)</f>
@@ -3756,9 +4246,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Power Alacrity Antiquary Staff Dagger Pistol</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Power Alacrity Antiquary Spear Axe Pistol</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3770,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>38512</v>
+        <v>38528</v>
       </c>
       <c r="E3">
         <f>ROUND(C3/D3*100,2)</f>
@@ -3791,21 +4281,21 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Antiquary Scepter Dagger Only</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Power Alacrity Antiquary Staff Dagger Pistol</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>38232</v>
+        <v>38512</v>
       </c>
       <c r="E4">
         <f>ROUND(C4/D4*100,2)</f>
@@ -3826,9 +4316,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Mirage Staff Axe Torch</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Antiquary Scepter Dagger Only</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3840,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>38199</v>
+        <v>38232</v>
       </c>
       <c r="E5">
         <f>ROUND(C5/D5*100,2)</f>
@@ -3856,14 +4346,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Evoker Pistol Warhorn</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Mirage Staff Axe Torch</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3875,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>38045</v>
+        <v>38199</v>
       </c>
       <c r="E6">
         <f>ROUND(C6/D6*100,2)</f>
@@ -3891,14 +4381,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Amalgam Steamshrieker Spear</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Evoker Pistol Warhorn</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3910,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>37433</v>
+        <v>38045</v>
       </c>
       <c r="E7">
         <f>ROUND(C7/D7*100,2)</f>
@@ -3926,26 +4416,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Power Alacrity Luminary Longbow Greatsword</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Amalgam Steamshrieker Spear</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>36532</v>
+        <v>37433</v>
       </c>
       <c r="E8">
         <f>ROUND(C8/D8*100,2)</f>
@@ -3961,14 +4451,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Power Alacrity Luminary Spear Greatsword</t>
+          <t>Power Alacrity Luminary Longbow Greatsword</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3980,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>36146</v>
+        <v>36532</v>
       </c>
       <c r="E9">
         <f>ROUND(C9/D9*100,2)</f>
@@ -4001,9 +4491,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Power Alacrity Antiquary Rifle Only</t>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Power Alacrity Luminary Spear Greatsword</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4015,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>36004</v>
+        <v>36146</v>
       </c>
       <c r="E10">
         <f>ROUND(C10/D10*100,2)</f>
@@ -4031,14 +4521,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Power Alacrity Bladesworn Overcharged Cartridges Sword Pistol</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Power Alacrity Antiquary Rifle Only</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4050,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>35556</v>
+        <v>36004</v>
       </c>
       <c r="E11">
         <f>ROUND(C11/D11*100,2)</f>
@@ -4066,26 +4556,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Power Boon Chronomancer Spear Dagger Sword</t>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Amalgam Two Kits Spear</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>35435</v>
+        <v>35846</v>
       </c>
       <c r="E12">
         <f>ROUND(C12/D12*100,2)</f>
@@ -4101,14 +4591,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Power Alacrity Amalgam Hammer</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Power Alacrity Bladesworn Overcharged Cartridges Sword Pistol</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4120,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>35416</v>
+        <v>35556</v>
       </c>
       <c r="E13">
         <f>ROUND(C13/D13*100,2)</f>
@@ -4136,26 +4626,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Specter Spear Only</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Power Boon Chronomancer Spear Dagger Sword</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>35026</v>
+        <v>35435</v>
       </c>
       <c r="E14">
         <f>ROUND(C14/D14*100,2)</f>
@@ -4171,14 +4661,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Power Boon Chronomancer Greatsword Spear</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Power Alacrity Amalgam Hammer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4190,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34826</v>
+        <v>35416</v>
       </c>
       <c r="E15">
         <f>ROUND(C15/D15*100,2)</f>
@@ -4206,26 +4696,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Power Boon Chronomancer Greatsword Dagger Sword</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Specter Spear Only</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>34824</v>
+        <v>35026</v>
       </c>
       <c r="E16">
         <f>ROUND(C16/D16*100,2)</f>
@@ -4241,14 +4731,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Power Alacrity Bladesworn Signets Sword Pistol</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Power Boon Chronomancer Greatsword Spear</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4260,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>34771</v>
+        <v>34826</v>
       </c>
       <c r="E17">
         <f>ROUND(C17/D17*100,2)</f>
@@ -4276,26 +4766,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Condition Boon Chronomancer Staff Scepter Torch</t>
+          <t>Power Boon Chronomancer Greatsword Dagger Sword</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>34701</v>
+        <v>34824</v>
       </c>
       <c r="E18">
         <f>ROUND(C18/D18*100,2)</f>
@@ -4316,21 +4806,21 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Renegade Spear Mace Axe</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Power Alacrity Bladesworn Signets Sword Pistol</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>34688</v>
+        <v>34771</v>
       </c>
       <c r="E19">
         <f>ROUND(C19/D19*100,2)</f>
@@ -4346,14 +4836,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Renegade Shortbow Mace Axe</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Condition Boon Chronomancer Staff Scepter Torch</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4365,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>34670</v>
+        <v>34701</v>
       </c>
       <c r="E20">
         <f>ROUND(C20/D20*100,2)</f>
@@ -4381,26 +4871,26 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Power Alacrity Tempest Hammer</t>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Renegade Spear Mace Axe</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>34518</v>
+        <v>34688</v>
       </c>
       <c r="E21">
         <f>ROUND(C21/D21*100,2)</f>
@@ -4416,26 +4906,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Power Alacrity Mechanist Two Kits Sword Pistol</t>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Renegade Shortbow Mace Axe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>34410</v>
+        <v>34670</v>
       </c>
       <c r="E22">
         <f>ROUND(C22/D22*100,2)</f>
@@ -4451,14 +4941,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Power Alacrity Evoker Scepter Dagger</t>
+          <t>Power Alacrity Tempest Hammer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4470,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>34372</v>
+        <v>34518</v>
       </c>
       <c r="E23">
         <f>ROUND(C23/D23*100,2)</f>
@@ -4491,9 +4981,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Specter Scepter Dagger Dagger</t>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Tempest Fire Only Scepter Focus</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4505,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>33853</v>
+        <v>34438</v>
       </c>
       <c r="E24">
         <f>ROUND(C24/D24*100,2)</f>
@@ -4521,14 +5011,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Power Alacrity Renegade Greatsword Sword Sword</t>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Power Alacrity Mechanist Two Kits Sword Pistol</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4540,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>33459</v>
+        <v>34410</v>
       </c>
       <c r="E25">
         <f>ROUND(C25/D25*100,2)</f>
@@ -4556,26 +5046,26 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Renegade Spear Only</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Power Alacrity Evoker Scepter Dagger</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>33300</v>
+        <v>34372</v>
       </c>
       <c r="E26">
         <f>ROUND(C26/D26*100,2)</f>
@@ -4591,26 +5081,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Power Alacrity Renegade Staff Sword Sword</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Tempest Pistol Warhorn</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>32850</v>
+        <v>34126</v>
       </c>
       <c r="E27">
         <f>ROUND(C27/D27*100,2)</f>
@@ -4626,26 +5116,26 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Power Alacrity Tempest Sword Dagger</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Specter Scepter Dagger Dagger</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>32500</v>
+        <v>33853</v>
       </c>
       <c r="E28">
         <f>ROUND(C28/D28*100,2)</f>
@@ -4661,14 +5151,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Condition Alacrity Scourge Scepter Torch Pistol</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Tempest Scepter Warhorn</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4680,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>32404</v>
+        <v>33647</v>
       </c>
       <c r="E29">
         <f>ROUND(C29/D29*100,2)</f>
@@ -4696,26 +5186,26 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Power Boon Chronomancer Greatsword Dagger Focus</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Specter Scepter Pistol Scepter Pistol</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>31888</v>
+        <v>33548</v>
       </c>
       <c r="E30">
         <f>ROUND(C30/D30*100,2)</f>
@@ -4731,14 +5221,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Power Alacrity Willbender Greatsword Sword Focus</t>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Power Alacrity Renegade Greatsword Sword Sword</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4750,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>31884</v>
+        <v>33459</v>
       </c>
       <c r="E31">
         <f>ROUND(C31/D31*100,2)</f>
@@ -4766,26 +5256,26 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Power Alacrity Willbender Spear Greatsword</t>
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Renegade Spear Only</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>31579</v>
+        <v>33300</v>
       </c>
       <c r="E32">
         <f>ROUND(C32/D32*100,2)</f>
@@ -4801,14 +5291,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>revenant</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Power Alacrity Mechanist Rifle</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Power Alacrity Paragon Sword Axe Dagger Mace</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4820,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>31193</v>
+        <v>33015</v>
       </c>
       <c r="E33">
         <f>ROUND(C33/D33*100,2)</f>
@@ -4836,14 +5326,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Celestial Alacrity Tempest Scepter Warhorn</t>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Power Alacrity Renegade Staff Sword Sword</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4855,7 +5345,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>21250</v>
+        <v>32850</v>
       </c>
       <c r="E34">
         <f>ROUND(C34/D34*100,2)</f>
@@ -4871,12 +5361,327 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>revenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Power Alacrity Tempest Sword Dagger</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>32500</v>
+      </c>
+      <c r="E35">
+        <f>ROUND(C35/D35*100,2)</f>
+        <v/>
+      </c>
+      <c r="F35">
+        <f>ROUND(D35*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>ROUND(F35-C35,0)</f>
+        <v/>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>elementalist</t>
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Scourge Scepter Torch Pistol</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>32404</v>
+      </c>
+      <c r="E36">
+        <f>ROUND(C36/D36*100,2)</f>
+        <v/>
+      </c>
+      <c r="F36">
+        <f>ROUND(D36*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>ROUND(F36-C36,0)</f>
+        <v/>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>necromancer</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Power Boon Chronomancer Greatsword Dagger Focus</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>31888</v>
+      </c>
+      <c r="E37">
+        <f>ROUND(C37/D37*100,2)</f>
+        <v/>
+      </c>
+      <c r="F37">
+        <f>ROUND(D37*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>ROUND(F37-C37,0)</f>
+        <v/>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>mesmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Power Alacrity Willbender Greatsword Sword Focus</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>31884</v>
+      </c>
+      <c r="E38">
+        <f>ROUND(C38/D38*100,2)</f>
+        <v/>
+      </c>
+      <c r="F38">
+        <f>ROUND(D38*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>ROUND(F38-C38,0)</f>
+        <v/>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Power Alacrity Willbender Spear Greatsword</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>31579</v>
+      </c>
+      <c r="E39">
+        <f>ROUND(C39/D39*100,2)</f>
+        <v/>
+      </c>
+      <c r="F39">
+        <f>ROUND(D39*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>ROUND(F39-C39,0)</f>
+        <v/>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Willbender Pistol Pistol Axe Torch</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>31223</v>
+      </c>
+      <c r="E40">
+        <f>ROUND(C40/D40*100,2)</f>
+        <v/>
+      </c>
+      <c r="F40">
+        <f>ROUND(D40*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>ROUND(F40-C40,0)</f>
+        <v/>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Power Alacrity Mechanist Rifle</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>31193</v>
+      </c>
+      <c r="E41">
+        <f>ROUND(C41/D41*100,2)</f>
+        <v/>
+      </c>
+      <c r="F41">
+        <f>ROUND(D41*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>ROUND(F41-C41,0)</f>
+        <v/>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Condition Alacrity Mechanist One Kit Pistol Pistol</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>30772</v>
+      </c>
+      <c r="E42">
+        <f>ROUND(C42/D42*100,2)</f>
+        <v/>
+      </c>
+      <c r="F42">
+        <f>ROUND(D42*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>ROUND(F42-C42,0)</f>
+        <v/>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Celestial Alacrity Tempest Scepter Warhorn</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>21250</v>
+      </c>
+      <c r="E43">
+        <f>ROUND(C43/D43*100,2)</f>
+        <v/>
+      </c>
+      <c r="F43">
+        <f>ROUND(D43*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G43">
+        <f>ROUND(F43-C43,0)</f>
+        <v/>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>elementalist</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G34"/>
+  <autoFilter ref="A1:G43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4887,7 +5692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
@@ -5006,7 +5811,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Power Quickness Deadeye Axe Pistol Dagger</t>
         </is>
@@ -5076,7 +5881,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Power Quickness Deadeye Dagger Only</t>
         </is>
@@ -5251,21 +6056,21 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Power Quickness Galeshot Longbow Axe Axe</t>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Condition Quickness Firebrand Axe Torch Pistol Pistol</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>35330</v>
+        <v>35420</v>
       </c>
       <c r="E11">
         <f>ROUND(C11/D11*100,2)</f>
@@ -5281,14 +6086,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>guardian</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Power Quickness Untamed Hammer Sword Axe</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Power Quickness Galeshot Longbow Axe Axe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5300,7 +6105,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>35258</v>
+        <v>35330</v>
       </c>
       <c r="E12">
         <f>ROUND(C12/D12*100,2)</f>
@@ -5321,9 +6126,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Power Quickness Berserker Greatsword Axe Axe</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Power Quickness Untamed Hammer Sword Axe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5335,7 +6140,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>35168</v>
+        <v>35258</v>
       </c>
       <c r="E13">
         <f>ROUND(C13/D13*100,2)</f>
@@ -5351,14 +6156,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Power Quickness Berserker Spear Axe Axe</t>
+          <t>Power Quickness Berserker Greatsword Axe Axe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5370,7 +6175,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>35096</v>
+        <v>35168</v>
       </c>
       <c r="E14">
         <f>ROUND(C14/D14*100,2)</f>
@@ -5391,9 +6196,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Power Quickness Catalyst Scepter Dagger</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Power Quickness Berserker Spear Axe Axe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5405,7 +6210,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>35068</v>
+        <v>35096</v>
       </c>
       <c r="E15">
         <f>ROUND(C15/D15*100,2)</f>
@@ -5421,26 +6226,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>warrior</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Condition Quickness Untamed Axe Dagger Dagger Torch</t>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Power Quickness Catalyst Scepter Dagger</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>35006</v>
+        <v>35068</v>
       </c>
       <c r="E16">
         <f>ROUND(C16/D16*100,2)</f>
@@ -5456,14 +6261,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Condition Quickness Scrapper Spear</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Condition Quickness Untamed Axe Dagger Dagger Torch</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5475,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>34765</v>
+        <v>35006</v>
       </c>
       <c r="E17">
         <f>ROUND(C17/D17*100,2)</f>
@@ -5491,14 +6296,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Power Quickness Conduit Staff Sword Sword</t>
+          <t>Power Quickness Conduit Greatsword Sword Sword</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5510,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>34511</v>
+        <v>34871</v>
       </c>
       <c r="E18">
         <f>ROUND(C18/D18*100,2)</f>
@@ -5531,9 +6336,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Power Quickness Untamed Nature Magic Hammer Sword Axe</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Power Boon Chronomancer Greatsword Spear</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5545,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>34281</v>
+        <v>34826</v>
       </c>
       <c r="E19">
         <f>ROUND(C19/D19*100,2)</f>
@@ -5561,26 +6366,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Condition Quickness Deadeye Spear Only</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Power Boon Chronomancer Greatsword Dagger Sword</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>34208</v>
+        <v>34824</v>
       </c>
       <c r="E20">
         <f>ROUND(C20/D20*100,2)</f>
@@ -5596,14 +6401,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Condition Quickness Conduit Spear Mace Axe</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Condition Quickness Scrapper Spear</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5615,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>34139</v>
+        <v>34765</v>
       </c>
       <c r="E21">
         <f>ROUND(C21/D21*100,2)</f>
@@ -5631,26 +6436,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>engineer</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Power Quickness Catalyst Sword Dagger</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Condition Boon Chronomancer Staff Scepter Torch</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>33825</v>
+        <v>34701</v>
       </c>
       <c r="E22">
         <f>ROUND(C22/D22*100,2)</f>
@@ -5666,14 +6471,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>mesmer</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Power Quickness Harbinger Greatsword Spear</t>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Power Quickness Conduit Staff Sword Sword</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5685,7 +6490,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>33646</v>
+        <v>34511</v>
       </c>
       <c r="E23">
         <f>ROUND(C23/D23*100,2)</f>
@@ -5701,26 +6506,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>necromancer</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Condition Quickness Catalyst Pistol Dagger</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Power Quickness Untamed Nature Magic Hammer Sword Axe</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>33356</v>
+        <v>34281</v>
       </c>
       <c r="E24">
         <f>ROUND(C24/D24*100,2)</f>
@@ -5736,26 +6541,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>elementalist</t>
+          <t>ranger</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Power Quickness Troubadour Spear Dagger Sword</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Condition Quickness Deadeye Spear Only</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>33000</v>
+        <v>34208</v>
       </c>
       <c r="E25">
         <f>ROUND(C25/D25*100,2)</f>
@@ -5771,26 +6576,26 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>mesmer</t>
+          <t>thief</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Power Quickness Deadeye Spear Only</t>
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Condition Quickness Conduit Spear Mace Axe</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>32221</v>
+        <v>34139</v>
       </c>
       <c r="E26">
         <f>ROUND(C26/D26*100,2)</f>
@@ -5806,14 +6611,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>thief</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Power Quickness Herald Greatsword Sword Sword</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Power Quickness Catalyst Sword Dagger</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5825,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>32154</v>
+        <v>33825</v>
       </c>
       <c r="E27">
         <f>ROUND(C27/D27*100,2)</f>
@@ -5841,26 +6646,26 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Condition Quickness Herald Spear Mace Axe</t>
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Power Quickness Harbinger Greatsword Spear</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>31339</v>
+        <v>33646</v>
       </c>
       <c r="E28">
         <f>ROUND(C28/D28*100,2)</f>
@@ -5876,14 +6681,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>necromancer</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Condition Quickness Herald Shortbow Mace Axe</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Condition Quickness Catalyst Pistol Warhorn</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5895,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>31289</v>
+        <v>33499</v>
       </c>
       <c r="E29">
         <f>ROUND(C29/D29*100,2)</f>
@@ -5911,26 +6716,26 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Power Quickness Herald Staff Sword Sword</t>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Condition Quickness Catalyst Pistol Dagger</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>30311</v>
+        <v>33356</v>
       </c>
       <c r="E30">
         <f>ROUND(C30/D30*100,2)</f>
@@ -5946,26 +6751,26 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>revenant</t>
+          <t>elementalist</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Condition Quickness Herald Spear Only</t>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Power Quickness Scrapper Hammer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>condition</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>29698</v>
+        <v>33015</v>
       </c>
       <c r="E31">
         <f>ROUND(C31/D31*100,2)</f>
@@ -5981,12 +6786,327 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Power Quickness Troubadour Spear Dagger Sword</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E32">
+        <f>ROUND(C32/D32*100,2)</f>
+        <v/>
+      </c>
+      <c r="F32">
+        <f>ROUND(D32*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>ROUND(F32-C32,0)</f>
+        <v/>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>mesmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Power Quickness Deadeye Spear Only</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>32221</v>
+      </c>
+      <c r="E33">
+        <f>ROUND(C33/D33*100,2)</f>
+        <v/>
+      </c>
+      <c r="F33">
+        <f>ROUND(D33*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>ROUND(F33-C33,0)</f>
+        <v/>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>thief</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Power Quickness Herald Greatsword Sword Sword</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>32154</v>
+      </c>
+      <c r="E34">
+        <f>ROUND(C34/D34*100,2)</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>ROUND(D34*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>ROUND(F34-C34,0)</f>
+        <v/>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>revenant</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Power Quickness Troubadour Spear Greatsword</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>32056</v>
+      </c>
+      <c r="E35">
+        <f>ROUND(C35/D35*100,2)</f>
+        <v/>
+      </c>
+      <c r="F35">
+        <f>ROUND(D35*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>ROUND(F35-C35,0)</f>
+        <v/>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>mesmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Power Boon Chronomancer Greatsword Dagger Focus</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>31888</v>
+      </c>
+      <c r="E36">
+        <f>ROUND(C36/D36*100,2)</f>
+        <v/>
+      </c>
+      <c r="F36">
+        <f>ROUND(D36*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>ROUND(F36-C36,0)</f>
+        <v/>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>mesmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Condition Quickness Herald Spear Mace Axe</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>31339</v>
+      </c>
+      <c r="E37">
+        <f>ROUND(C37/D37*100,2)</f>
+        <v/>
+      </c>
+      <c r="F37">
+        <f>ROUND(D37*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>ROUND(F37-C37,0)</f>
+        <v/>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>revenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Condition Quickness Herald Shortbow Mace Axe</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>31289</v>
+      </c>
+      <c r="E38">
+        <f>ROUND(C38/D38*100,2)</f>
+        <v/>
+      </c>
+      <c r="F38">
+        <f>ROUND(D38*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>ROUND(F38-C38,0)</f>
+        <v/>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>revenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Power Quickness Herald Staff Sword Sword</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>30311</v>
+      </c>
+      <c r="E39">
+        <f>ROUND(C39/D39*100,2)</f>
+        <v/>
+      </c>
+      <c r="F39">
+        <f>ROUND(D39*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>ROUND(F39-C39,0)</f>
+        <v/>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>revenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Condition Quickness Herald Spear Only</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>29698</v>
+      </c>
+      <c r="E40">
+        <f>ROUND(C40/D40*100,2)</f>
+        <v/>
+      </c>
+      <c r="F40">
+        <f>ROUND(D40*0.95,0)</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>ROUND(F40-C40,0)</f>
+        <v/>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>revenant</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G31"/>
+  <autoFilter ref="A1:G40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6079,7 +7199,7 @@
           <t>FF99FF99</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Ranger</t>
         </is>
@@ -6096,7 +7216,7 @@
           <t>FFB366FF</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Thief</t>
         </is>
